--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,6 +1954,986 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133756913</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>638412</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033809</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133757034</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033820</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133755993</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>638480</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7033801</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133757073</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>638303</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7033847</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133755848</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>638522</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7033819</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133755712</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>638602</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7033793</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133756916</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>638400</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7033819</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133755472</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>638707</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7033841</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133756944</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>638372</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7033789</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133756878</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>638416</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7033808</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>133755993</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92641</v>
+        <v>92643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R18" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R19" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>133755472</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>133756878</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,6 +2935,113 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133755347</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>638750</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7033849</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bohål i asp, 1.5m ovan mark.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133757034</v>
+        <v>133755993</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>91926</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638325</v>
+        <v>638480</v>
       </c>
       <c r="R15" t="n">
-        <v>7033820</v>
+        <v>7033801</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2130,11 +2125,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133755993</v>
+        <v>133757034</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2162,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638480</v>
+        <v>638325</v>
       </c>
       <c r="R16" t="n">
-        <v>7033801</v>
+        <v>7033820</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2232,6 +2227,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92643</v>
+        <v>92649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>133755993</v>
       </c>
       <c r="B15" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92649</v>
+        <v>92651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R18" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R19" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R18" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R19" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133755993</v>
+        <v>133757034</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638480</v>
+        <v>638325</v>
       </c>
       <c r="R15" t="n">
-        <v>7033801</v>
+        <v>7033820</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2125,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133757034</v>
+        <v>133755993</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,39 +2172,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638325</v>
+        <v>638480</v>
       </c>
       <c r="R16" t="n">
-        <v>7033820</v>
+        <v>7033801</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92651</v>
+        <v>92172</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R18" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R19" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>133755472</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>133756878</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>133755347</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>133757034</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>133755993</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92172</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>133755472</v>
       </c>
       <c r="B21" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>133756878</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>133755347</v>
       </c>
       <c r="B24" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133757034</v>
+        <v>133755993</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638325</v>
+        <v>638480</v>
       </c>
       <c r="R15" t="n">
-        <v>7033820</v>
+        <v>7033801</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2130,11 +2125,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133755993</v>
+        <v>133757034</v>
       </c>
       <c r="B16" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,34 +2162,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638480</v>
+        <v>638325</v>
       </c>
       <c r="R16" t="n">
-        <v>7033801</v>
+        <v>7033820</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2232,6 +2227,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R18" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R19" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133755993</v>
+        <v>133757034</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,34 +2065,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638480</v>
+        <v>638325</v>
       </c>
       <c r="R15" t="n">
-        <v>7033801</v>
+        <v>7033820</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2125,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133757034</v>
+        <v>133755993</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,39 +2172,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638325</v>
+        <v>638480</v>
       </c>
       <c r="R16" t="n">
-        <v>7033820</v>
+        <v>7033801</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2227,11 +2232,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133755848</v>
+        <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638522</v>
+        <v>638602</v>
       </c>
       <c r="R18" t="n">
-        <v>7033819</v>
+        <v>7033793</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133755712</v>
+        <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638602</v>
+        <v>638522</v>
       </c>
       <c r="R19" t="n">
-        <v>7033793</v>
+        <v>7033819</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
         <v>133756913</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>133755993</v>
       </c>
       <c r="B16" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>133757073</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>92184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>133755712</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>133755848</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>133756916</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>133755472</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>133756944</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>133756878</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 32076-2025 artfynd.xlsx
+++ b/artfynd/A 32076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712760</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712762</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712765</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712789</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754937</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755227</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755993</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1957,6 +2022,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133756913</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712766</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754841</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,6 +2438,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755120</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2450,6 +2540,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757073</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2547,6 +2642,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755234</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2644,6 +2744,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133756916</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2741,6 +2846,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133756944</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2838,6 +2948,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750648</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3032,6 +3152,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755472</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3129,6 +3254,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755848</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3226,6 +3356,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133756878</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3323,6 +3458,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757332</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3429,6 +3569,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712758</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3536,6 +3681,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755347</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3643,6 +3793,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3749,6 +3904,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712788</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3846,8 +4006,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>